--- a/Estates_AI_Programme_v4_3.xlsx
+++ b/Estates_AI_Programme_v4_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7675AF3E-EC07-4D2D-AC13-D24D446223A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252A6877-6FEF-40EE-8821-DC895BA996C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1426,6 +1426,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1433,15 +1442,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2105,29 +2105,29 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="17"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="14"/>
     </row>
     <row r="3" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -2520,29 +2520,29 @@
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="17"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="14"/>
     </row>
     <row r="10" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
@@ -3065,29 +3065,29 @@
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="17"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="14"/>
     </row>
     <row r="19" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
@@ -3220,29 +3220,29 @@
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="17"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13"/>
+      <c r="U21" s="14"/>
     </row>
     <row r="22" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -3635,29 +3635,29 @@
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="13"/>
-      <c r="U28" s="14"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
@@ -3790,29 +3790,29 @@
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="17"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="13"/>
+      <c r="U31" s="14"/>
     </row>
     <row r="32" spans="1:21" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
@@ -3825,10 +3825,10 @@
         <v>201</v>
       </c>
       <c r="D32" s="7">
+        <v>6</v>
+      </c>
+      <c r="E32" s="7">
         <v>8</v>
-      </c>
-      <c r="E32" s="7">
-        <v>10</v>
       </c>
       <c r="F32" s="7">
         <v>8</v>
@@ -3896,10 +3896,10 @@
         <v>4</v>
       </c>
       <c r="F33" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H33" s="7">
         <v>4</v>
@@ -4011,12 +4011,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A31:U31"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A9:U9"/>
     <mergeCell ref="A18:U18"/>
     <mergeCell ref="A21:U21"/>
     <mergeCell ref="A28:U28"/>
-    <mergeCell ref="A31:U31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4687,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7">
         <v>2</v>
